--- a/excel_upload_masters/templates/05_pipeline_requisitions_records.xlsx
+++ b/excel_upload_masters/templates/05_pipeline_requisitions_records.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="records" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="records" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,6 +433,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Joined</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nontaggd_campus</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Offered</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PIPELINE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>nontaggd_employee_referral</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Screening</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ON HOLD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nontaggd_internal_job_portal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&gt;10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Interview</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UNPROCESSED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>nontaggd_transferred</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Canceled</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CANCELLED</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>taggd_direct</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>taggd_rpo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:BN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -803,7 +978,11 @@
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
@@ -830,7 +1009,11 @@
           <t>JSON.</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
@@ -860,7 +1043,11 @@
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
       <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>Date/datetime — ISO-8601 or Excel date</t>
@@ -893,7 +1080,11 @@
       </c>
       <c r="BA2" s="2" t="inlineStr"/>
       <c r="BB2" s="2" t="inlineStr"/>
-      <c r="BC2" s="2" t="inlineStr"/>
+      <c r="BC2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="BD2" s="2" t="inlineStr"/>
       <c r="BE2" s="2" t="inlineStr"/>
       <c r="BF2" s="2" t="inlineStr"/>
@@ -919,6 +1110,20 @@
       <c r="BN2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="E3:E5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$A$1:$A$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$B$1:$B$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AT3:AT5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$C$1:$C$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="BC3:BC5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$D$1:$D$6</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>